--- a/public/templates/rpci_template.xlsx
+++ b/public/templates/rpci_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OCD CARAGA\Desktop\caraga-supply\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB33CDB-6CF8-441C-B3F7-E0A3FA7FC6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483E4866-BD71-48D0-8BB4-C20A1C461732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="599" xr2:uid="{F767CA18-B4B9-4566-8FC6-7F6BDE61727E}"/>
   </bookViews>
